--- a/tables/per_class.xlsx
+++ b/tables/per_class.xlsx
@@ -413,37 +413,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.8235294117647058</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="B2">
         <v>0.9696969696969697</v>
       </c>
       <c r="C2">
-        <v>0.9333333333333335</v>
+        <v>0.9285714285714287</v>
       </c>
       <c r="D2">
-        <v>0.9142857142857143</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E2">
-        <v>0.9333333333333333</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="F2">
-        <v>0.8235294117647058</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="G2">
-        <v>0.8749999999999999</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="H2">
         <v>0.34</v>
       </c>
       <c r="I2">
+        <v>0.26</v>
+      </c>
+      <c r="J2">
         <v>0.28</v>
       </c>
-      <c r="J2">
-        <v>0.3</v>
-      </c>
       <c r="K2">
-        <v>0.8966131907308378</v>
+        <v>0.8672014260249554</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="B4">
-        <v>0.78125</v>
+        <v>0.75</v>
       </c>
       <c r="C4">
-        <v>0.5882352941176471</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="D4">
-        <v>0.7575757575757577</v>
+        <v>0.7500000000000001</v>
       </c>
       <c r="E4">
-        <v>0.5882352941176471</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F4">
         <v>0.5555555555555556</v>
       </c>
       <c r="G4">
-        <v>0.5714285714285715</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="H4">
         <v>0.36</v>
@@ -510,10 +510,10 @@
         <v>0.2</v>
       </c>
       <c r="J4">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="K4">
-        <v>0.6684027777777778</v>
+        <v>0.6527777777777778</v>
       </c>
     </row>
   </sheetData>
